--- a/docs/daily_review_template.xlsx
+++ b/docs/daily_review_template.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="108">
   <si>
     <t xml:space="preserve">期货复盘日志 —— 使用说明</t>
   </si>
@@ -1394,7 +1394,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">是自动统计（用公式，不需要手填），按月汇总</t>
+      <t xml:space="preserve">是自动统计（用公式，不需要手填），按「品种</t>
     </r>
     <r>
       <rPr>
@@ -1405,7 +1405,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">composite</t>
+      <t xml:space="preserve">+</t>
     </r>
     <r>
       <rPr>
@@ -1415,7 +1415,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">结论的分布和留痕候选的次数，方便你自己评估这段时间系统给出的判断是偏多还是偏空、留痕的案例攒了多少条——这也是前面聊到的「系统到底准不准」的一种最简单的自查方式：多攒几个月的记录，回头对照实际走势，就能看出</t>
+      <t xml:space="preserve">月份」两个维度分别汇总</t>
     </r>
     <r>
       <rPr>
@@ -1436,7 +1436,91 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">的判断整体上站不站得住脚。</t>
+      <t xml:space="preserve">结论的分布和留痕候选的次数，不同品种的数据不会混在一起算——纯碱和豆粕的信号准不准是两回事，混着统计会互相掩盖。方便你自己评估某个品种在某段时间里系统给出的判断是偏多还是偏空、留痕的案例攒了多少条——这也是前面聊到的「系统到底准不准」的一种最简单的自查方式：多攒几个月的记录，回头对照实际走势，就能看出</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">composite</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的判断整体上站不站得住脚。现在预置的是</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SA/FG/M</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三个品种各</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个月，以后加了新品种，照抄一个品种的</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行、把「品种」列改成新代码就行，公式里引用的是这一行自己的品种和月份，不用跟着改。</t>
     </r>
   </si>
   <si>
@@ -1763,6 +1847,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">品种</t>
+  </si>
+  <si>
     <t xml:space="preserve">月份</t>
   </si>
   <si>
@@ -1779,6 +1866,9 @@
   </si>
   <si>
     <t xml:space="preserve">留痕候选次数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SA</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08</t>
@@ -1817,6 +1907,12 @@
     <t xml:space="preserve">2027-07</t>
   </si>
   <si>
+    <t xml:space="preserve">FG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -1825,7 +1921,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">说明：这张表全部是公式，跟着「每日复盘」</t>
+      <t xml:space="preserve">说明：这张表全部是公式，按「品种</t>
     </r>
     <r>
       <rPr>
@@ -1836,7 +1932,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">sheet</t>
+      <t xml:space="preserve">+</t>
     </r>
     <r>
       <rPr>
@@ -1846,7 +1942,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">自动更新，不需要手填。如果「每日复盘」以后加了更多行，需要把上面几个</t>
+      <t xml:space="preserve">月份」两个维度分别统计，跟着「每日复盘」</t>
     </r>
     <r>
       <rPr>
@@ -1857,7 +1953,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">SUMPRODUCT</t>
+      <t xml:space="preserve">sheet</t>
     </r>
     <r>
       <rPr>
@@ -1867,7 +1963,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">公式里的</t>
+      <t xml:space="preserve">自动更新，不需要手填，不同品种的数据不会混在一起算。以后加新品种，照抄一个品种的</t>
     </r>
     <r>
       <rPr>
@@ -1878,7 +1974,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">$A$3:$A$302</t>
+      <t xml:space="preserve">12</t>
     </r>
     <r>
       <rPr>
@@ -1888,7 +1984,70 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">等区域范围同步扩大。</t>
+      <t xml:space="preserve">行、把「品种」列改成新代码即可，公式引用的是这一行自己的品种和月份，不用跟着改；如果「每日复盘」以后加了超过</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">300</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行，需要把上面几个</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SUMPRODUCT</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公式里</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$3:$302</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">这个区域范围同步扩大。</t>
     </r>
   </si>
 </sst>
@@ -1896,10 +2055,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -2162,12 +2320,12 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -2686,7 +2844,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="8" t="s">
         <v>40</v>
       </c>
@@ -12838,11 +12996,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12859,41 +13017,47 @@
         <v>88</v>
       </c>
       <c r="E1" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>79</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>89</v>
       </c>
       <c r="G1" s="9" t="s">
         <v>90</v>
       </c>
+      <c r="H1" s="9" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B2" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A2)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
-        <v>0</v>
-      </c>
-      <c r="C2" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A2)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="D2" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A2)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="E2" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A2)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
-        <v>0</v>
-      </c>
-      <c r="F2" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A2)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
-        <v>0</v>
-      </c>
-      <c r="G2" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A2)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>92</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A2)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B2)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D2" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A2)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B2)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A2)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B2)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A2)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B2)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A2)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B2)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A2)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B2)*(每日复盘!$AC$3:$AC$302="是"))</f>
         <v>0</v>
       </c>
     </row>
@@ -12901,335 +13065,1137 @@
       <c r="A3" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="B3" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A3)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
-        <v>0</v>
-      </c>
-      <c r="C3" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A3)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="D3" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A3)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A3)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
-        <v>0</v>
-      </c>
-      <c r="F3" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A3)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A3)*(每日复盘!$AC$3:$AC$302="是"))</f>
+      <c r="B3" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A3)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B3)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A3)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B3)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A3)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B3)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A3)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B3)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A3)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B3)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A3)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B3)*(每日复盘!$AC$3:$AC$302="是"))</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B4" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A4)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
-        <v>0</v>
-      </c>
-      <c r="C4" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A4)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="D4" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A4)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="E4" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A4)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
-        <v>0</v>
-      </c>
-      <c r="F4" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A4)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
-        <v>0</v>
-      </c>
-      <c r="G4" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A4)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>92</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A4)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B4)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A4)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B4)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A4)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B4)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A4)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B4)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A4)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B4)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A4)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B4)*(每日复盘!$AC$3:$AC$302="是"))</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="B5" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A5)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
-        <v>0</v>
-      </c>
-      <c r="C5" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A5)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="D5" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A5)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A5)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A5)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A5)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>92</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A5)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B5)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A5)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B5)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A5)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B5)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A5)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B5)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A5)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B5)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A5)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B5)*(每日复盘!$AC$3:$AC$302="是"))</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B6" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A6)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
-        <v>0</v>
-      </c>
-      <c r="C6" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A6)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A6)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A6)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A6)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A6)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>92</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A6)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B6)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A6)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B6)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A6)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B6)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A6)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B6)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A6)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B6)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A6)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B6)*(每日复盘!$AC$3:$AC$302="是"))</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B7" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A7)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A7)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A7)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A7)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A7)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A7)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>92</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A7)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B7)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A7)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B7)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A7)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B7)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A7)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B7)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A7)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B7)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A7)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B7)*(每日复盘!$AC$3:$AC$302="是"))</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B8" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A8)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A8)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A8)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A8)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A8)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A8)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>92</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A8)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B8)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A8)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B8)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A8)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B8)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A8)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B8)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A8)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B8)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A8)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B8)*(每日复盘!$AC$3:$AC$302="是"))</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B9" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A9)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
-        <v>0</v>
-      </c>
-      <c r="C9" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A9)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A9)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A9)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A9)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A9)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>92</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A9)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B9)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A9)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B9)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A9)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B9)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A9)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B9)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A9)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B9)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A9)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B9)*(每日复盘!$AC$3:$AC$302="是"))</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B10" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A10)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A10)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A10)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A10)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A10)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A10)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>92</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A10)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B10)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A10)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B10)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A10)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B10)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A10)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B10)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A10)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B10)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A10)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B10)*(每日复盘!$AC$3:$AC$302="是"))</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="B11" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A11)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A11)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A11)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A11)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A11)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A11)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>92</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A11)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B11)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A11)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B11)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A11)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B11)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A11)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B11)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A11)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B11)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A11)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B11)*(每日复盘!$AC$3:$AC$302="是"))</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B12" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A12)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A12)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A12)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A12)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A12)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A12)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>92</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A12)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B12)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A12)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B12)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A12)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B12)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A12)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B12)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A12)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B12)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A12)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B12)*(每日复盘!$AC$3:$AC$302="是"))</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A13)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B13)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A13)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B13)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A13)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B13)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A13)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B13)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A13)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B13)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A13)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B13)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A14)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B14)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A14)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B14)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A14)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B14)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A14)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B14)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A14)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B14)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A14)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B14)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A15)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B15)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A15)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B15)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A15)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B15)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A15)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B15)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A15)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B15)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A15)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B15)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A16)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B16)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A16)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B16)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A16)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B16)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A16)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B16)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A16)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B16)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A16)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B16)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A17)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B17)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A17)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B17)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A17)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B17)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A17)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B17)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A17)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B17)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A17)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B17)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A18)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B18)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A18)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B18)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A18)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B18)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A18)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B18)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A18)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B18)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A18)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B18)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A19)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B19)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A19)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B19)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A19)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B19)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A19)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B19)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A19)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B19)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A19)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B19)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A20)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B20)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A20)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B20)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A20)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B20)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A20)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B20)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A20)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B20)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A20)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B20)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A21)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B21)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A21)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B21)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A21)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B21)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A21)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B21)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A21)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B21)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A21)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B21)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A22)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B22)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A22)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B22)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A22)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B22)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A22)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B22)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A22)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B22)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A22)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B22)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A13)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A13)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A13)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A13)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A13)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="17" t="n">
-        <f aca="false">SUMPRODUCT((TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=A13)*(每日复盘!$AC$3:$AC$302="是"))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
+      <c r="C23" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A23)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B23)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A23)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B23)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A23)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B23)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A23)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B23)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A23)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B23)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A23)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B23)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B24" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
+      <c r="C24" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A24)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B24)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A24)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B24)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A24)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B24)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A24)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B24)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A24)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B24)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A24)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B24)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A25)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B25)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A25)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B25)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A25)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B25)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A25)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B25)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A25)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B25)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A25)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B25)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A26)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B26)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A26)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B26)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A26)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B26)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A26)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B26)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A26)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B26)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A26)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B26)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A27)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B27)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A27)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B27)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A27)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B27)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A27)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B27)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A27)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B27)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H27" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A27)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B27)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A28)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B28)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A28)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B28)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A28)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B28)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A28)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B28)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A28)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B28)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H28" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A28)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B28)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A29)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B29)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A29)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B29)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A29)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B29)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A29)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B29)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A29)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B29)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H29" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A29)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B29)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A30)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B30)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D30" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A30)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B30)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A30)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B30)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A30)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B30)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A30)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B30)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H30" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A30)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B30)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A31)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B31)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D31" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A31)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B31)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A31)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B31)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A31)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B31)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A31)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B31)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H31" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A31)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B31)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A32)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B32)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D32" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A32)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B32)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A32)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B32)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A32)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B32)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A32)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B32)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H32" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A32)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B32)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A33)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B33)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A33)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B33)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A33)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B33)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A33)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B33)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G33" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A33)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B33)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H33" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A33)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B33)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A34)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B34)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A34)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B34)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A34)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B34)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A34)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B34)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A34)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B34)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A34)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B34)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C35" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A35)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B35)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D35" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A35)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B35)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A35)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B35)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A35)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B35)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G35" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A35)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B35)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H35" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A35)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B35)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A36)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B36)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A36)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B36)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A36)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B36)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A36)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B36)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A36)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B36)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H36" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A36)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B36)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A37)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B37)*(每日复盘!$A$3:$A$302&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="D37" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A37)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B37)*(每日复盘!$T$3:$T$302="多头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A37)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B37)*(每日复盘!$T$3:$T$302="空头因素占优"))</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A37)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B37)*(每日复盘!$T$3:$T$302="多空信号不一致"))</f>
+        <v>0</v>
+      </c>
+      <c r="G37" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A37)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B37)*(每日复盘!$T$3:$T$302="无明显方向"))</f>
+        <v>0</v>
+      </c>
+      <c r="H37" s="16" t="n">
+        <f aca="false">SUMPRODUCT((每日复盘!$B$3:$B$302=A37)*(TEXT(每日复盘!$A$3:$A$302,"yyyy-mm")=B37)*(每日复盘!$AC$3:$AC$302="是"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A39:H39"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
